--- a/exports/trend_1d/HINDPETRO_full_report.xlsx
+++ b/exports/trend_1d/HINDPETRO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>13.37</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="H2" t="n">
-        <v>60.65</v>
+        <v>59.45</v>
       </c>
       <c r="I2" t="n">
         <v>60.574252369596</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>0.75</v>
+        <v>-1.25</v>
       </c>
       <c r="L2" t="n">
         <v>5.73</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>19.2</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42065</v>
+        <v>42066</v>
       </c>
       <c r="H3" t="n">
-        <v>70.34999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>70.36753362180458</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>-18.33</v>
+        <v>-18.76</v>
       </c>
       <c r="L3" t="n">
-        <v>19.68</v>
+        <v>21.03</v>
       </c>
       <c r="M3" t="n">
         <v>5.26</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>15.04</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42118</v>
+        <v>42121</v>
       </c>
       <c r="H4" t="n">
-        <v>66.3</v>
+        <v>62.25</v>
       </c>
       <c r="I4" t="n">
         <v>64.05259218922964</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.09</v>
+        <v>-11.83</v>
       </c>
       <c r="L4" t="n">
-        <v>9.92</v>
+        <v>13.88</v>
       </c>
       <c r="M4" t="n">
         <v>0.72</v>
       </c>
       <c r="N4" t="n">
-        <v>4.12</v>
+        <v>6.11</v>
       </c>
       <c r="O4" t="n">
         <v>0.36</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>17.23</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42152</v>
+        <v>42153</v>
       </c>
       <c r="H5" t="n">
-        <v>67.84999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="I5" t="n">
         <v>70.47211880965423</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K5" t="n">
-        <v>-9</v>
+        <v>-17.59</v>
       </c>
       <c r="L5" t="n">
-        <v>10.68</v>
+        <v>18.47</v>
       </c>
       <c r="M5" t="n">
-        <v>3.18</v>
+        <v>5.16</v>
       </c>
       <c r="N5" t="n">
-        <v>6.19</v>
+        <v>7.89</v>
       </c>
       <c r="O5" t="n">
         <v>-6.11</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>14.24</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42227</v>
+        <v>42228</v>
       </c>
       <c r="H6" t="n">
-        <v>111.55</v>
+        <v>101.6</v>
       </c>
       <c r="I6" t="n">
         <v>102.4567971984309</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K6" t="n">
-        <v>52.39</v>
+        <v>38.8</v>
       </c>
       <c r="L6" t="n">
         <v>4.3</v>
@@ -783,7 +854,7 @@
         <v>0.87</v>
       </c>
       <c r="N6" t="n">
-        <v>2.67</v>
+        <v>8.92</v>
       </c>
       <c r="O6" t="n">
         <v>7.89</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>19.51</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42335</v>
+        <v>42338</v>
       </c>
       <c r="H7" t="n">
-        <v>92.05</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>92.44890914405673</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K7" t="n">
-        <v>9.4</v>
+        <v>5.66</v>
       </c>
       <c r="L7" t="n">
         <v>10.58</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>11.22</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42388</v>
+        <v>42389</v>
       </c>
       <c r="H8" t="n">
-        <v>93.7</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>92.62202489001623</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.24</v>
+        <v>-4.9</v>
       </c>
       <c r="L8" t="n">
-        <v>6.1</v>
+        <v>8.24</v>
       </c>
       <c r="M8" t="n">
         <v>1.7</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>14.45</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42432</v>
+        <v>42433</v>
       </c>
       <c r="H9" t="n">
-        <v>80.84999999999999</v>
+        <v>83.25</v>
       </c>
       <c r="I9" t="n">
         <v>82.68980184785781</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K9" t="n">
-        <v>11.3</v>
+        <v>8.67</v>
       </c>
       <c r="L9" t="n">
         <v>4</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>17.88</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42604</v>
+        <v>42605</v>
       </c>
       <c r="H10" t="n">
-        <v>147.4</v>
+        <v>138.5</v>
       </c>
       <c r="I10" t="n">
         <v>141.0897438040394</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K10" t="n">
-        <v>77.06</v>
+        <v>66.37</v>
       </c>
       <c r="L10" t="n">
         <v>4.98</v>
@@ -1011,7 +1130,7 @@
         <v>2.92</v>
       </c>
       <c r="N10" t="n">
-        <v>4.28</v>
+        <v>6.04</v>
       </c>
       <c r="O10" t="n">
         <v>2.97</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>16.02</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42643</v>
+        <v>42646</v>
       </c>
       <c r="H11" t="n">
-        <v>155.15</v>
+        <v>158.7</v>
       </c>
       <c r="I11" t="n">
         <v>157.7460591033381</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K11" t="n">
-        <v>-12.02</v>
+        <v>-14.58</v>
       </c>
       <c r="L11" t="n">
         <v>15.27</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.31</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42718</v>
+        <v>42719</v>
       </c>
       <c r="H12" t="n">
-        <v>159.3</v>
+        <v>156.4</v>
       </c>
       <c r="I12" t="n">
         <v>156.4816420494003</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K12" t="n">
-        <v>0.38</v>
+        <v>-1.45</v>
       </c>
       <c r="L12" t="n">
         <v>7.4</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>13.66</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="H13" t="n">
-        <v>165.9</v>
+        <v>171.75</v>
       </c>
       <c r="I13" t="n">
         <v>167.4298349847338</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K13" t="n">
-        <v>-6.07</v>
+        <v>-9.81</v>
       </c>
       <c r="L13" t="n">
-        <v>6.75</v>
+        <v>10.9</v>
       </c>
       <c r="M13" t="n">
         <v>0.96</v>
       </c>
       <c r="N13" t="n">
-        <v>3.11</v>
+        <v>3.53</v>
       </c>
       <c r="O13" t="n">
         <v>-1.82</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.96</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42780</v>
+        <v>42781</v>
       </c>
       <c r="H14" t="n">
-        <v>205.5</v>
+        <v>196.8</v>
       </c>
       <c r="I14" t="n">
         <v>198.302211386227</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K14" t="n">
-        <v>19.65</v>
+        <v>14.59</v>
       </c>
       <c r="L14" t="n">
         <v>3.41</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>14.16</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42837</v>
+        <v>42838</v>
       </c>
       <c r="H15" t="n">
-        <v>204</v>
+        <v>210.9</v>
       </c>
       <c r="I15" t="n">
         <v>206.531438093712</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.66</v>
+        <v>-7.16</v>
       </c>
       <c r="L15" t="n">
         <v>10.44</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>9.77</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42859</v>
+        <v>42860</v>
       </c>
       <c r="H16" t="n">
-        <v>199.45</v>
+        <v>196.15</v>
       </c>
       <c r="I16" t="n">
         <v>196.2942722384479</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.43</v>
+        <v>-6.99</v>
       </c>
       <c r="L16" t="n">
-        <v>7.04</v>
+        <v>7.4</v>
       </c>
       <c r="M16" t="n">
         <v>0.79</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>11.44</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42880</v>
+        <v>42881</v>
       </c>
       <c r="H17" t="n">
-        <v>190.1</v>
+        <v>214.3</v>
       </c>
       <c r="I17" t="n">
         <v>202.8853029157426</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K17" t="n">
-        <v>3.08</v>
+        <v>-9.25</v>
       </c>
       <c r="L17" t="n">
-        <v>5.56</v>
+        <v>10.4</v>
       </c>
       <c r="M17" t="n">
         <v>1.6</v>
       </c>
       <c r="N17" t="n">
-        <v>2.01</v>
+        <v>12.73</v>
       </c>
       <c r="O17" t="n">
         <v>-1.65</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>18.19</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H18" t="n">
-        <v>251.5</v>
+        <v>243.25</v>
       </c>
       <c r="I18" t="n">
         <v>246.7563932210626</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K18" t="n">
-        <v>17.36</v>
+        <v>13.51</v>
       </c>
       <c r="L18" t="n">
         <v>14.79</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>15.75</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43024</v>
+        <v>43025</v>
       </c>
       <c r="H19" t="n">
-        <v>265</v>
+        <v>271.35</v>
       </c>
       <c r="I19" t="n">
         <v>267.9420317403811</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K19" t="n">
-        <v>-8.94</v>
+        <v>-11.55</v>
       </c>
       <c r="L19" t="n">
-        <v>10.03</v>
+        <v>12.35</v>
       </c>
       <c r="M19" t="n">
         <v>3.23</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>11.46</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43048</v>
+        <v>43049</v>
       </c>
       <c r="H20" t="n">
-        <v>247.15</v>
+        <v>238.1</v>
       </c>
       <c r="I20" t="n">
         <v>245.3229871398663</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K20" t="n">
-        <v>-8.92</v>
+        <v>-12.25</v>
       </c>
       <c r="L20" t="n">
-        <v>11.89</v>
+        <v>12.73</v>
       </c>
       <c r="M20" t="n">
         <v>0.77</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,25 +1868,25 @@
         <v>15.4</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43083</v>
+        <v>43084</v>
       </c>
       <c r="H21" t="n">
-        <v>250.7</v>
+        <v>254.75</v>
       </c>
       <c r="I21" t="n">
         <v>253.7312750781335</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.29</v>
+        <v>-6.99</v>
       </c>
       <c r="L21" t="n">
-        <v>5.61</v>
+        <v>7.73</v>
       </c>
       <c r="M21" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="N21" t="n">
         <v>4.16</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,25 +1937,25 @@
         <v>9.16</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43119</v>
+        <v>43122</v>
       </c>
       <c r="H22" t="n">
-        <v>237.65</v>
+        <v>228.75</v>
       </c>
       <c r="I22" t="n">
         <v>231.4197580720815</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.71</v>
+        <v>-10.21</v>
       </c>
       <c r="L22" t="n">
-        <v>10.38</v>
+        <v>11.05</v>
       </c>
       <c r="M22" t="n">
-        <v>0.92</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
         <v>3.98</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>11.14</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43266</v>
+        <v>43269</v>
       </c>
       <c r="H23" t="n">
-        <v>169.8</v>
+        <v>179.55</v>
       </c>
       <c r="I23" t="n">
         <v>179.3641056474694</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K23" t="n">
-        <v>25.77</v>
+        <v>21.51</v>
       </c>
       <c r="L23" t="n">
         <v>3.5</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>6</v>
+      </c>
+      <c r="U23" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>11.76</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43277</v>
+        <v>43278</v>
       </c>
       <c r="H24" t="n">
-        <v>165.35</v>
+        <v>151.45</v>
       </c>
       <c r="I24" t="n">
         <v>158.4295342913497</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K24" t="n">
-        <v>-7.91</v>
+        <v>-15.65</v>
       </c>
       <c r="L24" t="n">
-        <v>8.970000000000001</v>
+        <v>16.71</v>
       </c>
       <c r="M24" t="n">
-        <v>1.14</v>
+        <v>1.69</v>
       </c>
       <c r="N24" t="n">
-        <v>4.37</v>
+        <v>8.41</v>
       </c>
       <c r="O24" t="n">
         <v>5.74</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>18.4</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43308</v>
+        <v>43311</v>
       </c>
       <c r="H25" t="n">
-        <v>155.75</v>
+        <v>158.25</v>
       </c>
       <c r="I25" t="n">
         <v>158.115787555012</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.84</v>
+        <v>-4.49</v>
       </c>
       <c r="L25" t="n">
         <v>7.33</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>11.39</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43333</v>
+        <v>43335</v>
       </c>
       <c r="H26" t="n">
-        <v>145.4</v>
+        <v>140.9</v>
       </c>
       <c r="I26" t="n">
         <v>143.5103764154637</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K26" t="n">
-        <v>-8.119999999999999</v>
+        <v>-10.96</v>
       </c>
       <c r="L26" t="n">
-        <v>8.75</v>
+        <v>11.44</v>
       </c>
       <c r="M26" t="n">
         <v>1.83</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>13.08</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43396</v>
+        <v>43397</v>
       </c>
       <c r="H27" t="n">
-        <v>115.15</v>
+        <v>124.3</v>
       </c>
       <c r="I27" t="n">
         <v>123.6768182142689</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K27" t="n">
-        <v>18.28</v>
+        <v>11.78</v>
       </c>
       <c r="L27" t="n">
         <v>2.84</v>
       </c>
       <c r="M27" t="n">
-        <v>4.22</v>
+        <v>4.82</v>
       </c>
       <c r="N27" t="n">
         <v>18.34</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>26.01</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43497</v>
+        <v>43500</v>
       </c>
       <c r="H28" t="n">
-        <v>125.1</v>
+        <v>120.5</v>
       </c>
       <c r="I28" t="n">
         <v>123.1293610241874</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K28" t="n">
-        <v>0.64</v>
+        <v>-3.06</v>
       </c>
       <c r="L28" t="n">
         <v>8.289999999999999</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>11.91</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H29" t="n">
-        <v>124.3</v>
+        <v>133</v>
       </c>
       <c r="I29" t="n">
         <v>126.597465097966</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.15</v>
+        <v>-10.37</v>
       </c>
       <c r="L29" t="n">
-        <v>6.56</v>
+        <v>11.08</v>
       </c>
       <c r="M29" t="n">
         <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>4.85</v>
+        <v>7</v>
       </c>
       <c r="O29" t="n">
         <v>-3.68</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>15.02</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43558</v>
+        <v>43559</v>
       </c>
       <c r="H30" t="n">
-        <v>141.45</v>
+        <v>140.4</v>
       </c>
       <c r="I30" t="n">
         <v>140.9860094785884</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K30" t="n">
-        <v>6.35</v>
+        <v>5.56</v>
       </c>
       <c r="L30" t="n">
         <v>7.14</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>14.57</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43580</v>
+        <v>43581</v>
       </c>
       <c r="H31" t="n">
-        <v>150.45</v>
+        <v>155.3</v>
       </c>
       <c r="I31" t="n">
         <v>154.3192808129763</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K31" t="n">
-        <v>-7.16</v>
+        <v>-10.61</v>
       </c>
       <c r="L31" t="n">
-        <v>8.9</v>
+        <v>11.11</v>
       </c>
       <c r="M31" t="n">
         <v>1.33</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>14.1</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43644</v>
+        <v>43647</v>
       </c>
       <c r="H32" t="n">
-        <v>159.7</v>
+        <v>155.1</v>
       </c>
       <c r="I32" t="n">
         <v>158.3649306851891</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K32" t="n">
-        <v>2.83</v>
+        <v>-0.13</v>
       </c>
       <c r="L32" t="n">
         <v>9.08</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>12.81</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43704</v>
+        <v>43705</v>
       </c>
       <c r="H33" t="n">
-        <v>141</v>
+        <v>144.25</v>
       </c>
       <c r="I33" t="n">
         <v>142.193361310994</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K33" t="n">
-        <v>9.09</v>
+        <v>7</v>
       </c>
       <c r="L33" t="n">
         <v>7.45</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>16.33</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43782</v>
+        <v>43783</v>
       </c>
       <c r="H34" t="n">
-        <v>160.55</v>
+        <v>158.75</v>
       </c>
       <c r="I34" t="n">
         <v>160.4764095372024</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K34" t="n">
-        <v>11.3</v>
+        <v>10.05</v>
       </c>
       <c r="L34" t="n">
         <v>8.84</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>12.47</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43938</v>
+        <v>43941</v>
       </c>
       <c r="H35" t="n">
-        <v>115.05</v>
+        <v>121</v>
       </c>
       <c r="I35" t="n">
         <v>117.0279666063593</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K35" t="n">
-        <v>27.53</v>
+        <v>23.78</v>
       </c>
       <c r="L35" t="n">
         <v>5.45</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>23.92</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43966</v>
+        <v>43969</v>
       </c>
       <c r="H36" t="n">
-        <v>97.34999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I36" t="n">
         <v>92.05948184222575</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K36" t="n">
-        <v>-19.55</v>
+        <v>-28.02</v>
       </c>
       <c r="L36" t="n">
-        <v>20.79</v>
+        <v>28.88</v>
       </c>
       <c r="M36" t="n">
         <v>7.65</v>
       </c>
       <c r="N36" t="n">
-        <v>6.6</v>
+        <v>10.53</v>
       </c>
       <c r="O36" t="n">
         <v>5.17</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>30.25</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43987</v>
+        <v>43990</v>
       </c>
       <c r="H37" t="n">
-        <v>106.95</v>
+        <v>114.25</v>
       </c>
       <c r="I37" t="n">
         <v>110.0809734149992</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K37" t="n">
-        <v>-22.79</v>
+        <v>-31.17</v>
       </c>
       <c r="L37" t="n">
-        <v>23.36</v>
+        <v>35.48</v>
       </c>
       <c r="M37" t="n">
         <v>2.93</v>
       </c>
       <c r="N37" t="n">
-        <v>5.73</v>
+        <v>6.83</v>
       </c>
       <c r="O37" t="n">
         <v>-10.53</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>16.24</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44026</v>
+        <v>44027</v>
       </c>
       <c r="H38" t="n">
-        <v>110.55</v>
+        <v>105.75</v>
       </c>
       <c r="I38" t="n">
         <v>107.0704676317567</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.24</v>
+        <v>-7.44</v>
       </c>
       <c r="L38" t="n">
         <v>9.23</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>17.81</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44032</v>
+        <v>44033</v>
       </c>
       <c r="H39" t="n">
-        <v>120.85</v>
+        <v>125.25</v>
       </c>
       <c r="I39" t="n">
         <v>124.2674688792742</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>-14.28</v>
+        <v>-18.44</v>
       </c>
       <c r="L39" t="n">
-        <v>15.7</v>
+        <v>20.66</v>
       </c>
       <c r="M39" t="n">
         <v>1.4</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>16.7</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44074</v>
+        <v>44075</v>
       </c>
       <c r="H40" t="n">
-        <v>105.05</v>
+        <v>103.9</v>
       </c>
       <c r="I40" t="n">
         <v>104.5858800514774</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K40" t="n">
-        <v>-16.13</v>
+        <v>-17.05</v>
       </c>
       <c r="L40" t="n">
-        <v>16.69</v>
+        <v>19.48</v>
       </c>
       <c r="M40" t="n">
         <v>1.48</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>12.37</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44133</v>
+        <v>44134</v>
       </c>
       <c r="H41" t="n">
-        <v>91.55</v>
+        <v>96.5</v>
       </c>
       <c r="I41" t="n">
         <v>95.08257770764544</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K41" t="n">
-        <v>11.89</v>
+        <v>7.12</v>
       </c>
       <c r="L41" t="n">
         <v>3.08</v>
       </c>
       <c r="M41" t="n">
-        <v>1.76</v>
+        <v>3.28</v>
       </c>
       <c r="N41" t="n">
         <v>5.53</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>14.24</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H42" t="n">
-        <v>119.15</v>
+        <v>109.85</v>
       </c>
       <c r="I42" t="n">
         <v>110.9422307628804</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K42" t="n">
-        <v>23.47</v>
+        <v>13.83</v>
       </c>
       <c r="L42" t="n">
         <v>4.2</v>
       </c>
       <c r="M42" t="n">
-        <v>0.58</v>
+        <v>0.97</v>
       </c>
       <c r="N42" t="n">
-        <v>2.32</v>
+        <v>7.81</v>
       </c>
       <c r="O42" t="n">
         <v>5.41</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>16.17</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44209</v>
+        <v>44210</v>
       </c>
       <c r="H43" t="n">
-        <v>120.85</v>
+        <v>124.85</v>
       </c>
       <c r="I43" t="n">
         <v>123.6376573964742</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>-10.01</v>
+        <v>-13.65</v>
       </c>
       <c r="L43" t="n">
-        <v>13.25</v>
+        <v>14.7</v>
       </c>
       <c r="M43" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="N43" t="n">
-        <v>1.9</v>
+        <v>3.31</v>
       </c>
       <c r="O43" t="n">
         <v>-7.81</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>10.36</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44384</v>
+        <v>44385</v>
       </c>
       <c r="H44" t="n">
-        <v>169.8</v>
+        <v>155.9</v>
       </c>
       <c r="I44" t="n">
         <v>157.0911186247419</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K44" t="n">
-        <v>36</v>
+        <v>24.87</v>
       </c>
       <c r="L44" t="n">
         <v>10.53</v>
       </c>
       <c r="M44" t="n">
-        <v>2.61</v>
+        <v>7.74</v>
       </c>
       <c r="N44" t="n">
-        <v>4.75</v>
+        <v>8.19</v>
       </c>
       <c r="O44" t="n">
         <v>3.31</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>7</v>
+      </c>
+      <c r="U44" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>11.13</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44441</v>
+        <v>44442</v>
       </c>
       <c r="H45" t="n">
-        <v>145.3</v>
+        <v>151</v>
       </c>
       <c r="I45" t="n">
         <v>145.5129612955397</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K45" t="n">
-        <v>6.8</v>
+        <v>3.14</v>
       </c>
       <c r="L45" t="n">
         <v>2.21</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.02</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44501</v>
+        <v>44502</v>
       </c>
       <c r="H46" t="n">
-        <v>173.25</v>
+        <v>168</v>
       </c>
       <c r="I46" t="n">
         <v>169.8961865301835</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K46" t="n">
-        <v>14.74</v>
+        <v>11.26</v>
       </c>
       <c r="L46" t="n">
         <v>4.01</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>14.56</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44504</v>
+        <v>44508</v>
       </c>
       <c r="H47" t="n">
-        <v>179.4</v>
+        <v>194.2</v>
       </c>
       <c r="I47" t="n">
         <v>192.463158395473</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.79</v>
+        <v>-15.6</v>
       </c>
       <c r="L47" t="n">
-        <v>7.17</v>
+        <v>16.04</v>
       </c>
       <c r="M47" t="n">
         <v>1.69</v>
       </c>
       <c r="N47" t="n">
-        <v>3.96</v>
+        <v>8.25</v>
       </c>
       <c r="O47" t="n">
         <v>-3.03</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>15.71</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H48" t="n">
-        <v>180.5</v>
+        <v>176.35</v>
       </c>
       <c r="I48" t="n">
         <v>178.0201348914626</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K48" t="n">
-        <v>-7.05</v>
+        <v>-9.19</v>
       </c>
       <c r="L48" t="n">
-        <v>7.75</v>
+        <v>10.07</v>
       </c>
       <c r="M48" t="n">
         <v>0.64</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>12.93</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H49" t="n">
-        <v>164.55</v>
+        <v>174.75</v>
       </c>
       <c r="I49" t="n">
         <v>171.6530678783679</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K49" t="n">
-        <v>6.69</v>
+        <v>0.91</v>
       </c>
       <c r="L49" t="n">
         <v>4.99</v>
@@ -3234,7 +3821,7 @@
         <v>1.1</v>
       </c>
       <c r="N49" t="n">
-        <v>2.65</v>
+        <v>6.2</v>
       </c>
       <c r="O49" t="n">
         <v>-2.3</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>11.7</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H50" t="n">
-        <v>172.35</v>
+        <v>168.05</v>
       </c>
       <c r="I50" t="n">
         <v>168.1941348783781</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.37</v>
+        <v>-3.83</v>
       </c>
       <c r="L50" t="n">
         <v>5.81</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>11.96</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44659</v>
+        <v>44662</v>
       </c>
       <c r="H51" t="n">
-        <v>163.65</v>
+        <v>166.85</v>
       </c>
       <c r="I51" t="n">
         <v>165.6732738259408</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K51" t="n">
-        <v>2.62</v>
+        <v>0.71</v>
       </c>
       <c r="L51" t="n">
         <v>7.02</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>11.25</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44679</v>
+        <v>44680</v>
       </c>
       <c r="H52" t="n">
-        <v>154.85</v>
+        <v>147.55</v>
       </c>
       <c r="I52" t="n">
         <v>148.0821443660813</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.19</v>
+        <v>-11.57</v>
       </c>
       <c r="L52" t="n">
-        <v>8.6</v>
+        <v>11.69</v>
       </c>
       <c r="M52" t="n">
         <v>1.46</v>
       </c>
       <c r="N52" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="O52" t="n">
         <v>1.96</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>15.75</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44748</v>
+        <v>44749</v>
       </c>
       <c r="H53" t="n">
-        <v>125</v>
+        <v>131.7</v>
       </c>
       <c r="I53" t="n">
         <v>126.2124852304157</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K53" t="n">
-        <v>15.28</v>
+        <v>10.74</v>
       </c>
       <c r="L53" t="n">
         <v>6.64</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>13.97</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44796</v>
+        <v>44797</v>
       </c>
       <c r="H54" t="n">
-        <v>130.35</v>
+        <v>127.55</v>
       </c>
       <c r="I54" t="n">
         <v>129.9162601108725</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.03</v>
+        <v>-3.15</v>
       </c>
       <c r="L54" t="n">
         <v>9.19</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>11.69</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44888</v>
+        <v>44889</v>
       </c>
       <c r="H55" t="n">
-        <v>113.05</v>
+        <v>117.35</v>
       </c>
       <c r="I55" t="n">
         <v>116.1036088485068</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K55" t="n">
-        <v>11.37</v>
+        <v>8</v>
       </c>
       <c r="L55" t="n">
         <v>8.27</v>
@@ -3576,7 +4235,7 @@
         <v>2.06</v>
       </c>
       <c r="N55" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="O55" t="n">
         <v>-2.15</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>9.15</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44958</v>
+        <v>44959</v>
       </c>
       <c r="H56" t="n">
-        <v>126</v>
+        <v>122.75</v>
       </c>
       <c r="I56" t="n">
         <v>124.8141502311566</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K56" t="n">
-        <v>7.37</v>
+        <v>4.6</v>
       </c>
       <c r="L56" t="n">
         <v>3.03</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>12.37</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45000</v>
+        <v>45001</v>
       </c>
       <c r="H57" t="n">
-        <v>122.8</v>
+        <v>131.55</v>
       </c>
       <c r="I57" t="n">
         <v>124.3571877610131</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.04</v>
+        <v>-7.17</v>
       </c>
       <c r="L57" t="n">
-        <v>3.26</v>
+        <v>8.43</v>
       </c>
       <c r="M57" t="n">
         <v>1.45</v>
       </c>
       <c r="N57" t="n">
-        <v>2.35</v>
+        <v>7.13</v>
       </c>
       <c r="O57" t="n">
         <v>-2.58</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>11.07</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="H58" t="n">
-        <v>126.8</v>
+        <v>119.85</v>
       </c>
       <c r="I58" t="n">
         <v>120.5211908091207</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.61</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>6.65</v>
+        <v>11.4</v>
       </c>
       <c r="M58" t="n">
-        <v>0.67</v>
+        <v>3.27</v>
       </c>
       <c r="N58" t="n">
-        <v>1.84</v>
+        <v>5.48</v>
       </c>
       <c r="O58" t="n">
         <v>7.13</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>10.9</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45036</v>
+        <v>45037</v>
       </c>
       <c r="H59" t="n">
-        <v>128.6</v>
+        <v>129.9</v>
       </c>
       <c r="I59" t="n">
         <v>129.7655288430038</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K59" t="n">
-        <v>-7.3</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="L59" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="M59" t="n">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="N59" t="n">
         <v>4.89</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45134</v>
+        <v>45135</v>
       </c>
       <c r="H60" t="n">
-        <v>160.15</v>
+        <v>153.15</v>
       </c>
       <c r="I60" t="n">
         <v>153.3508170688218</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K60" t="n">
-        <v>23.29</v>
+        <v>17.9</v>
       </c>
       <c r="L60" t="n">
         <v>1.54</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>13.93</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45236</v>
+        <v>45237</v>
       </c>
       <c r="H61" t="n">
-        <v>142.45</v>
+        <v>152.7</v>
       </c>
       <c r="I61" t="n">
         <v>144.2128421493074</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K61" t="n">
-        <v>6.99</v>
+        <v>0.29</v>
       </c>
       <c r="L61" t="n">
         <v>5.26</v>
@@ -3918,7 +4649,7 @@
         <v>2.74</v>
       </c>
       <c r="N61" t="n">
-        <v>2.8</v>
+        <v>7.2</v>
       </c>
       <c r="O61" t="n">
         <v>-4.37</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>13.26</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H62" t="n">
-        <v>307.5</v>
+        <v>288.75</v>
       </c>
       <c r="I62" t="n">
         <v>292.3648928885618</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K62" t="n">
-        <v>101.38</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L62" t="n">
         <v>7.53</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>5</v>
+      </c>
+      <c r="U62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>17.18</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="H63" t="n">
-        <v>295.85</v>
+        <v>319.4</v>
       </c>
       <c r="I63" t="n">
         <v>303.3848219445019</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.46</v>
+        <v>-10.61</v>
       </c>
       <c r="L63" t="n">
-        <v>7.08</v>
+        <v>11.32</v>
       </c>
       <c r="M63" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="N63" t="n">
-        <v>6.48</v>
+        <v>7.96</v>
       </c>
       <c r="O63" t="n">
         <v>-6.1</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>14.14</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H64" t="n">
-        <v>349.6</v>
+        <v>295.5</v>
       </c>
       <c r="I64" t="n">
         <v>308.1578520449573</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K64" t="n">
-        <v>9.460000000000001</v>
+        <v>-7.48</v>
       </c>
       <c r="L64" t="n">
-        <v>11.24</v>
+        <v>12.65</v>
       </c>
       <c r="M64" t="n">
         <v>1.28</v>
       </c>
       <c r="N64" t="n">
-        <v>4.36</v>
+        <v>15.47</v>
       </c>
       <c r="O64" t="n">
         <v>7.96</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>26.52</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45497</v>
+        <v>45498</v>
       </c>
       <c r="H65" t="n">
-        <v>317.75</v>
+        <v>336.2</v>
       </c>
       <c r="I65" t="n">
         <v>321.9111983442863</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K65" t="n">
-        <v>-7.53</v>
+        <v>-13.77</v>
       </c>
       <c r="L65" t="n">
         <v>18.75</v>
@@ -4146,7 +4925,7 @@
         <v>3.38</v>
       </c>
       <c r="N65" t="n">
-        <v>4.61</v>
+        <v>5.81</v>
       </c>
       <c r="O65" t="n">
         <v>-15.47</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>15.25</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45545</v>
+        <v>45546</v>
       </c>
       <c r="H66" t="n">
-        <v>390.5</v>
+        <v>379.45</v>
       </c>
       <c r="I66" t="n">
         <v>380.0914166173109</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K66" t="n">
-        <v>16.15</v>
+        <v>12.86</v>
       </c>
       <c r="L66" t="n">
         <v>7.35</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>13.92</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45561</v>
+        <v>45562</v>
       </c>
       <c r="H67" t="n">
-        <v>391</v>
+        <v>405.85</v>
       </c>
       <c r="I67" t="n">
         <v>403.2217805026534</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.04</v>
+        <v>-6.96</v>
       </c>
       <c r="L67" t="n">
-        <v>6.47</v>
+        <v>7.41</v>
       </c>
       <c r="M67" t="n">
         <v>1.86</v>
       </c>
       <c r="N67" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="O67" t="n">
         <v>-2.83</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>10.84</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H68" t="n">
-        <v>377.05</v>
+        <v>364.8</v>
       </c>
       <c r="I68" t="n">
         <v>373.5497203506005</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K68" t="n">
-        <v>-7.1</v>
+        <v>-10.11</v>
       </c>
       <c r="L68" t="n">
-        <v>9.779999999999999</v>
+        <v>10.73</v>
       </c>
       <c r="M68" t="n">
         <v>3.58</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>13.64</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="H69" t="n">
-        <v>370.4</v>
+        <v>375.2</v>
       </c>
       <c r="I69" t="n">
         <v>370.548418003756</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.54</v>
+        <v>-2.85</v>
       </c>
       <c r="L69" t="n">
         <v>11.53</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>8.35</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H70" t="n">
-        <v>360</v>
+        <v>337.7</v>
       </c>
       <c r="I70" t="n">
         <v>356.5039492127907</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K70" t="n">
-        <v>-4.05</v>
+        <v>-9.99</v>
       </c>
       <c r="L70" t="n">
-        <v>6.25</v>
+        <v>11.05</v>
       </c>
       <c r="M70" t="n">
-        <v>1.52</v>
+        <v>3.07</v>
       </c>
       <c r="N70" t="n">
-        <v>5.84</v>
+        <v>6.19</v>
       </c>
       <c r="O70" t="n">
         <v>1.3</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>12.63</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H71" t="n">
-        <v>302.25</v>
+        <v>314.3</v>
       </c>
       <c r="I71" t="n">
         <v>304.810952195684</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K71" t="n">
-        <v>10.5</v>
+        <v>6.93</v>
       </c>
       <c r="L71" t="n">
         <v>4.26</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>13.23</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45869</v>
+        <v>45870</v>
       </c>
       <c r="H72" t="n">
-        <v>387.75</v>
+        <v>374.2</v>
       </c>
       <c r="I72" t="n">
         <v>385.0181723014237</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K72" t="n">
-        <v>23.37</v>
+        <v>19.06</v>
       </c>
       <c r="L72" t="n">
         <v>5.79</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>6</v>
+      </c>
+      <c r="U72" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>11.06</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="H73" t="n">
-        <v>385.8</v>
+        <v>388.6</v>
       </c>
       <c r="I73" t="n">
         <v>386.565810930579</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K73" t="n">
-        <v>-3.1</v>
+        <v>-3.85</v>
       </c>
       <c r="L73" t="n">
         <v>4.26</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>5.66</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="H74" t="n">
-        <v>429.8</v>
+        <v>428.4</v>
       </c>
       <c r="I74" t="n">
         <v>429.3703794579381</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K74" t="n">
-        <v>10.6</v>
+        <v>10.24</v>
       </c>
       <c r="L74" t="n">
         <v>0.91</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>4</v>
+      </c>
+      <c r="U74" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>7.98</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="H75" t="n">
-        <v>445.8</v>
+        <v>474.6</v>
       </c>
       <c r="I75" t="n">
         <v>454.0217672341237</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K75" t="n">
-        <v>-4.06</v>
+        <v>-10.78</v>
       </c>
       <c r="L75" t="n">
-        <v>6.72</v>
+        <v>11.19</v>
       </c>
       <c r="M75" t="n">
         <v>0.67</v>
       </c>
       <c r="N75" t="n">
-        <v>2.64</v>
+        <v>6.46</v>
       </c>
       <c r="O75" t="n">
         <v>-0.33</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>9.83</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="H76" t="n">
-        <v>453.1</v>
+        <v>430.05</v>
       </c>
       <c r="I76" t="n">
         <v>440.6913627781584</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.53</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>6.02</v>
+        <v>10.04</v>
       </c>
       <c r="M76" t="n">
-        <v>0.14</v>
+        <v>0.3</v>
       </c>
       <c r="N76" t="n">
-        <v>2.04</v>
+        <v>5.09</v>
       </c>
       <c r="O76" t="n">
         <v>6.46</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>11.41</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H77" t="n">
-        <v>428.6</v>
+        <v>436.35</v>
       </c>
       <c r="I77" t="n">
         <v>433.8703827582531</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K77" t="n">
-        <v>0.34</v>
+        <v>-1.46</v>
       </c>
       <c r="L77" t="n">
         <v>5.21</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>11.52</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H78" t="n">
-        <v>403.7</v>
+        <v>381.8</v>
       </c>
       <c r="I78" t="n">
         <v>400.3849604283617</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K78" t="n">
-        <v>-7.48</v>
+        <v>-12.5</v>
       </c>
       <c r="L78" t="n">
-        <v>9.35</v>
+        <v>12.8</v>
       </c>
       <c r="M78" t="n">
         <v>4.03</v>
       </c>
       <c r="N78" t="n">
-        <v>4.97</v>
+        <v>5.42</v>
       </c>
       <c r="O78" t="n">
         <v>1.81</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>12.75</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="H79" t="n">
-        <v>352.7</v>
+        <v>360.9</v>
       </c>
       <c r="I79" t="n">
         <v>357.8413053797674</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K79" t="n">
-        <v>7.62</v>
+        <v>5.47</v>
       </c>
       <c r="L79" t="n">
         <v>6.23</v>
@@ -4953,7 +5900,19 @@
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>13.38</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="H80" t="n">
-        <v>361.35</v>
+        <v>356.5</v>
       </c>
       <c r="I80" t="n">
         <v>358.8713457126278</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K80" t="n">
-        <v>0.12</v>
+        <v>-1.22</v>
       </c>
       <c r="L80" t="n">
         <v>6.25</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>6</v>
+      </c>
+      <c r="U80" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -5061,6 +6032,14 @@
       <c r="Q81" t="n">
         <v>36</v>
       </c>
+      <c r="R81" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10019,7 +10998,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.1</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="6">
@@ -10029,7 +11008,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -10039,7 +11018,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8">
@@ -10049,7 +11028,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -10059,7 +11038,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65.5</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="10">
@@ -10069,7 +11048,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>109.4</v>
+        <v>112.4</v>
       </c>
     </row>
     <row r="11">
@@ -10079,7 +11058,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -10089,7 +11068,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -10099,7 +11078,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36.7</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="14">
@@ -10109,7 +11088,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.46</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="15">
@@ -10119,7 +11098,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.17</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="16">
@@ -10129,7 +11108,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.64</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="17">
@@ -10139,7 +11118,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>101.38</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -10149,7 +11128,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -10159,7 +11138,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.050000000000001</v>
+        <v>9.640000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -10169,7 +11148,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.14</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="21">
@@ -10179,7 +11158,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23.36</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="22">
@@ -10189,7 +11168,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23">
@@ -10199,7 +11178,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
@@ -10209,7 +11188,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="25">
@@ -10229,7 +11208,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.35</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="27">
@@ -10249,7 +11228,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29">
